--- a/artfynd/A 42118-2020 artfynd.xlsx
+++ b/artfynd/A 42118-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42118-2020 artfynd.xlsx
+++ b/artfynd/A 42118-2020 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119826322</v>
+        <v>119826323</v>
       </c>
       <c r="B7" t="n">
-        <v>91844</v>
+        <v>91834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618249</v>
+        <v>618224</v>
       </c>
       <c r="R7" t="n">
-        <v>7278455</v>
+        <v>7278444</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119826327</v>
+        <v>119826325</v>
       </c>
       <c r="B8" t="n">
         <v>91834</v>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618212</v>
+        <v>618204</v>
       </c>
       <c r="R8" t="n">
-        <v>7278495</v>
+        <v>7278490</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119826325</v>
+        <v>119826327</v>
       </c>
       <c r="B9" t="n">
         <v>91834</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618204</v>
+        <v>618212</v>
       </c>
       <c r="R9" t="n">
-        <v>7278490</v>
+        <v>7278495</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119826326</v>
+        <v>119826328</v>
       </c>
       <c r="B10" t="n">
         <v>91463</v>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618209</v>
+        <v>618225</v>
       </c>
       <c r="R10" t="n">
-        <v>7278497</v>
+        <v>7278499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119826320</v>
+        <v>119826329</v>
       </c>
       <c r="B11" t="n">
         <v>91834</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618286</v>
+        <v>618226</v>
       </c>
       <c r="R11" t="n">
-        <v>7278489</v>
+        <v>7278508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119826324</v>
+        <v>119826330</v>
       </c>
       <c r="B12" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618163</v>
+        <v>618249</v>
       </c>
       <c r="R12" t="n">
-        <v>7278453</v>
+        <v>7278528</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119826329</v>
+        <v>119826326</v>
       </c>
       <c r="B14" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618226</v>
+        <v>618209</v>
       </c>
       <c r="R14" t="n">
-        <v>7278508</v>
+        <v>7278497</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119826328</v>
+        <v>119826322</v>
       </c>
       <c r="B15" t="n">
-        <v>91463</v>
+        <v>91844</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,25 +2063,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618225</v>
+        <v>618249</v>
       </c>
       <c r="R15" t="n">
-        <v>7278499</v>
+        <v>7278455</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119826323</v>
+        <v>119826320</v>
       </c>
       <c r="B16" t="n">
         <v>91834</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618224</v>
+        <v>618286</v>
       </c>
       <c r="R16" t="n">
-        <v>7278444</v>
+        <v>7278489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119826330</v>
+        <v>119826324</v>
       </c>
       <c r="B17" t="n">
-        <v>91834</v>
+        <v>91828</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2267,25 +2267,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618249</v>
+        <v>618163</v>
       </c>
       <c r="R17" t="n">
-        <v>7278528</v>
+        <v>7278453</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 42118-2020 artfynd.xlsx
+++ b/artfynd/A 42118-2020 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119826323</v>
+        <v>119826322</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91844</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618224</v>
+        <v>618249</v>
       </c>
       <c r="R7" t="n">
-        <v>7278444</v>
+        <v>7278455</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119826327</v>
+        <v>119826330</v>
       </c>
       <c r="B9" t="n">
         <v>91834</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618212</v>
+        <v>618249</v>
       </c>
       <c r="R9" t="n">
-        <v>7278495</v>
+        <v>7278528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119826328</v>
+        <v>119826326</v>
       </c>
       <c r="B10" t="n">
         <v>91463</v>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618225</v>
+        <v>618209</v>
       </c>
       <c r="R10" t="n">
-        <v>7278499</v>
+        <v>7278497</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119826330</v>
+        <v>119826320</v>
       </c>
       <c r="B12" t="n">
         <v>91834</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618249</v>
+        <v>618286</v>
       </c>
       <c r="R12" t="n">
-        <v>7278528</v>
+        <v>7278489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119826321</v>
+        <v>119826327</v>
       </c>
       <c r="B13" t="n">
         <v>91834</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618275</v>
+        <v>618212</v>
       </c>
       <c r="R13" t="n">
-        <v>7278473</v>
+        <v>7278495</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119826326</v>
+        <v>119826328</v>
       </c>
       <c r="B14" t="n">
         <v>91463</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618209</v>
+        <v>618225</v>
       </c>
       <c r="R14" t="n">
-        <v>7278497</v>
+        <v>7278499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119826322</v>
+        <v>119826324</v>
       </c>
       <c r="B15" t="n">
-        <v>91844</v>
+        <v>91828</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4365</v>
+        <v>149</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618249</v>
+        <v>618163</v>
       </c>
       <c r="R15" t="n">
-        <v>7278455</v>
+        <v>7278453</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119826320</v>
+        <v>119826321</v>
       </c>
       <c r="B16" t="n">
         <v>91834</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618286</v>
+        <v>618275</v>
       </c>
       <c r="R16" t="n">
-        <v>7278489</v>
+        <v>7278473</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119826324</v>
+        <v>119826323</v>
       </c>
       <c r="B17" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2267,25 +2267,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618163</v>
+        <v>618224</v>
       </c>
       <c r="R17" t="n">
-        <v>7278453</v>
+        <v>7278444</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 42118-2020 artfynd.xlsx
+++ b/artfynd/A 42118-2020 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119826322</v>
+        <v>119826325</v>
       </c>
       <c r="B7" t="n">
-        <v>91844</v>
+        <v>91834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618249</v>
+        <v>618204</v>
       </c>
       <c r="R7" t="n">
-        <v>7278455</v>
+        <v>7278490</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119826325</v>
+        <v>119826321</v>
       </c>
       <c r="B8" t="n">
         <v>91834</v>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618204</v>
+        <v>618275</v>
       </c>
       <c r="R8" t="n">
-        <v>7278490</v>
+        <v>7278473</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119826330</v>
+        <v>119826327</v>
       </c>
       <c r="B9" t="n">
         <v>91834</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618249</v>
+        <v>618212</v>
       </c>
       <c r="R9" t="n">
-        <v>7278528</v>
+        <v>7278495</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119826326</v>
+        <v>119826328</v>
       </c>
       <c r="B10" t="n">
         <v>91463</v>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618209</v>
+        <v>618225</v>
       </c>
       <c r="R10" t="n">
-        <v>7278497</v>
+        <v>7278499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119826329</v>
+        <v>119826324</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>91828</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,25 +1655,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618226</v>
+        <v>618163</v>
       </c>
       <c r="R11" t="n">
-        <v>7278508</v>
+        <v>7278453</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119826320</v>
+        <v>119826329</v>
       </c>
       <c r="B12" t="n">
         <v>91834</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618286</v>
+        <v>618226</v>
       </c>
       <c r="R12" t="n">
-        <v>7278489</v>
+        <v>7278508</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119826327</v>
+        <v>119826330</v>
       </c>
       <c r="B13" t="n">
         <v>91834</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618212</v>
+        <v>618249</v>
       </c>
       <c r="R13" t="n">
-        <v>7278495</v>
+        <v>7278528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119826328</v>
+        <v>119826326</v>
       </c>
       <c r="B14" t="n">
         <v>91463</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618225</v>
+        <v>618209</v>
       </c>
       <c r="R14" t="n">
-        <v>7278499</v>
+        <v>7278497</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119826324</v>
+        <v>119826323</v>
       </c>
       <c r="B15" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,25 +2063,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618163</v>
+        <v>618224</v>
       </c>
       <c r="R15" t="n">
-        <v>7278453</v>
+        <v>7278444</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119826321</v>
+        <v>119826320</v>
       </c>
       <c r="B16" t="n">
         <v>91834</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618275</v>
+        <v>618286</v>
       </c>
       <c r="R16" t="n">
-        <v>7278473</v>
+        <v>7278489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119826323</v>
+        <v>119826322</v>
       </c>
       <c r="B17" t="n">
-        <v>91834</v>
+        <v>91844</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2267,25 +2267,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618224</v>
+        <v>618249</v>
       </c>
       <c r="R17" t="n">
-        <v>7278444</v>
+        <v>7278455</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 42118-2020 artfynd.xlsx
+++ b/artfynd/A 42118-2020 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119826325</v>
+        <v>119826323</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618204</v>
+        <v>618224</v>
       </c>
       <c r="R7" t="n">
-        <v>7278490</v>
+        <v>7278444</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119826321</v>
+        <v>119826322</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>91862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,25 +1349,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618275</v>
+        <v>618249</v>
       </c>
       <c r="R8" t="n">
-        <v>7278473</v>
+        <v>7278455</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119826327</v>
+        <v>119826328</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618212</v>
+        <v>618225</v>
       </c>
       <c r="R9" t="n">
-        <v>7278495</v>
+        <v>7278499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119826328</v>
+        <v>119826329</v>
       </c>
       <c r="B10" t="n">
-        <v>91463</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618225</v>
+        <v>618226</v>
       </c>
       <c r="R10" t="n">
-        <v>7278499</v>
+        <v>7278508</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119826324</v>
+        <v>119826326</v>
       </c>
       <c r="B11" t="n">
-        <v>91828</v>
+        <v>91481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,25 +1655,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>149</v>
+        <v>4745</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618163</v>
+        <v>618209</v>
       </c>
       <c r="R11" t="n">
-        <v>7278453</v>
+        <v>7278497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119826329</v>
+        <v>119826327</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618226</v>
+        <v>618212</v>
       </c>
       <c r="R12" t="n">
-        <v>7278508</v>
+        <v>7278495</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119826330</v>
+        <v>119826325</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618249</v>
+        <v>618204</v>
       </c>
       <c r="R13" t="n">
-        <v>7278528</v>
+        <v>7278490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119826326</v>
+        <v>119826321</v>
       </c>
       <c r="B14" t="n">
-        <v>91463</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618209</v>
+        <v>618275</v>
       </c>
       <c r="R14" t="n">
-        <v>7278497</v>
+        <v>7278473</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119826323</v>
+        <v>119826330</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618224</v>
+        <v>618249</v>
       </c>
       <c r="R15" t="n">
-        <v>7278444</v>
+        <v>7278528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119826320</v>
+        <v>119826324</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,25 +2165,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618286</v>
+        <v>618163</v>
       </c>
       <c r="R16" t="n">
-        <v>7278489</v>
+        <v>7278453</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119826322</v>
+        <v>119826320</v>
       </c>
       <c r="B17" t="n">
-        <v>91844</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2267,25 +2267,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618249</v>
+        <v>618286</v>
       </c>
       <c r="R17" t="n">
-        <v>7278455</v>
+        <v>7278489</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 42118-2020 artfynd.xlsx
+++ b/artfynd/A 42118-2020 artfynd.xlsx
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119826323</v>
+        <v>119826321</v>
       </c>
       <c r="B7" t="n">
         <v>91852</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618224</v>
+        <v>618275</v>
       </c>
       <c r="R7" t="n">
-        <v>7278444</v>
+        <v>7278473</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119826322</v>
+        <v>119826329</v>
       </c>
       <c r="B8" t="n">
-        <v>91862</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,25 +1349,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618249</v>
+        <v>618226</v>
       </c>
       <c r="R8" t="n">
-        <v>7278455</v>
+        <v>7278508</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119826328</v>
+        <v>119826326</v>
       </c>
       <c r="B9" t="n">
         <v>91481</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618225</v>
+        <v>618209</v>
       </c>
       <c r="R9" t="n">
-        <v>7278499</v>
+        <v>7278497</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119826329</v>
+        <v>119826323</v>
       </c>
       <c r="B10" t="n">
         <v>91852</v>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618226</v>
+        <v>618224</v>
       </c>
       <c r="R10" t="n">
-        <v>7278508</v>
+        <v>7278444</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119826326</v>
+        <v>119826320</v>
       </c>
       <c r="B11" t="n">
-        <v>91481</v>
+        <v>91852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,21 +1659,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618209</v>
+        <v>618286</v>
       </c>
       <c r="R11" t="n">
-        <v>7278497</v>
+        <v>7278489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119826327</v>
+        <v>119826325</v>
       </c>
       <c r="B12" t="n">
         <v>91852</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618212</v>
+        <v>618204</v>
       </c>
       <c r="R12" t="n">
-        <v>7278495</v>
+        <v>7278490</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119826325</v>
+        <v>119826322</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,25 +1859,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618204</v>
+        <v>618249</v>
       </c>
       <c r="R13" t="n">
-        <v>7278490</v>
+        <v>7278455</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119826321</v>
+        <v>119826327</v>
       </c>
       <c r="B14" t="n">
         <v>91852</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618275</v>
+        <v>618212</v>
       </c>
       <c r="R14" t="n">
-        <v>7278473</v>
+        <v>7278495</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2153,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119826324</v>
+        <v>119826328</v>
       </c>
       <c r="B16" t="n">
-        <v>91846</v>
+        <v>91481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,25 +2165,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>149</v>
+        <v>4745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618163</v>
+        <v>618225</v>
       </c>
       <c r="R16" t="n">
-        <v>7278453</v>
+        <v>7278499</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119826320</v>
+        <v>119826324</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>91846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2267,25 +2267,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618286</v>
+        <v>618163</v>
       </c>
       <c r="R17" t="n">
-        <v>7278489</v>
+        <v>7278453</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 42118-2020 artfynd.xlsx
+++ b/artfynd/A 42118-2020 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119826321</v>
+        <v>119826322</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618275</v>
+        <v>618249</v>
       </c>
       <c r="R7" t="n">
-        <v>7278473</v>
+        <v>7278455</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119826329</v>
+        <v>119826327</v>
       </c>
       <c r="B8" t="n">
         <v>91852</v>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>618226</v>
+        <v>618212</v>
       </c>
       <c r="R8" t="n">
-        <v>7278508</v>
+        <v>7278495</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119826326</v>
+        <v>119826320</v>
       </c>
       <c r="B9" t="n">
-        <v>91481</v>
+        <v>91852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618209</v>
+        <v>618286</v>
       </c>
       <c r="R9" t="n">
-        <v>7278497</v>
+        <v>7278489</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119826323</v>
+        <v>119826326</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>91481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618224</v>
+        <v>618209</v>
       </c>
       <c r="R10" t="n">
-        <v>7278444</v>
+        <v>7278497</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119826320</v>
+        <v>119826325</v>
       </c>
       <c r="B11" t="n">
         <v>91852</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618286</v>
+        <v>618204</v>
       </c>
       <c r="R11" t="n">
-        <v>7278489</v>
+        <v>7278490</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119826325</v>
+        <v>119826329</v>
       </c>
       <c r="B12" t="n">
         <v>91852</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618204</v>
+        <v>618226</v>
       </c>
       <c r="R12" t="n">
-        <v>7278490</v>
+        <v>7278508</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119826322</v>
+        <v>119826324</v>
       </c>
       <c r="B13" t="n">
-        <v>91862</v>
+        <v>91846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>149</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618249</v>
+        <v>618163</v>
       </c>
       <c r="R13" t="n">
-        <v>7278455</v>
+        <v>7278453</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119826327</v>
+        <v>119826328</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>91481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618212</v>
+        <v>618225</v>
       </c>
       <c r="R14" t="n">
-        <v>7278495</v>
+        <v>7278499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119826330</v>
+        <v>119826321</v>
       </c>
       <c r="B15" t="n">
         <v>91852</v>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618249</v>
+        <v>618275</v>
       </c>
       <c r="R15" t="n">
-        <v>7278528</v>
+        <v>7278473</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119826328</v>
+        <v>119826330</v>
       </c>
       <c r="B16" t="n">
-        <v>91481</v>
+        <v>91852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618225</v>
+        <v>618249</v>
       </c>
       <c r="R16" t="n">
-        <v>7278499</v>
+        <v>7278528</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119826324</v>
+        <v>119826323</v>
       </c>
       <c r="B17" t="n">
-        <v>91846</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2267,25 +2267,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618163</v>
+        <v>618224</v>
       </c>
       <c r="R17" t="n">
-        <v>7278453</v>
+        <v>7278444</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
